--- a/02_DIA_inicio_2026_analisis_assets/rbd_9704_escuela-lo-valledor_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9704_escuela-lo-valledor_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{902083DE-8FAF-4B18-9D58-7198444A3425}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A980309C-8EFA-4FE9-96F3-2216819C8E66}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9FBFF20-57F7-4764-9186-1E680E6D2474}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8901334A-FEB0-490F-A513-6AB8F9797C11}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C38165-F9CF-4136-9C52-B043ACD573EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD9606CF-1E7C-42A6-BCC5-28D831732589}"/>
 </file>